--- a/docs-v2/template/template_import_classification_rules.xlsx
+++ b/docs-v2/template/template_import_classification_rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\pacman\e-dashbord\docs-v2\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84A05F16-8B6F-4FF6-A04F-EB182723BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6901BEC8-8893-4324-A368-9B6DD8F1A8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2688" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Klasifikasi Item" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
   <si>
     <t>Template Import Klasifikasi Item</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>PART</t>
+  </si>
+  <si>
+    <t>LABEL</t>
+  </si>
+  <si>
+    <t>PAPER</t>
+  </si>
+  <si>
+    <t>CARD</t>
+  </si>
+  <si>
+    <t>card</t>
   </si>
 </sst>
 </file>
@@ -492,8 +504,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.796875" customWidth="1"/>
     <col min="2" max="2" width="30.796875" customWidth="1"/>
@@ -533,7 +545,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -544,7 +556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -555,7 +567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -566,7 +578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -577,133 +589,133 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
@@ -711,12 +723,45 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>25</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
         <v>27</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C23" t="s">
         <v>15</v>
       </c>
     </row>
